--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1086,12 +1086,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -945,12 +945,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO21"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,130 +513,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Odd_D_HT</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Odd_A_HT</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over05</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under05</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Over15</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>HT_Odd_Under15</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>FT_Odd_Over05</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over15</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under15</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Odd_Over35</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under35</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>homeGoals</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>awayGoals</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Odd_H_D</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Odd_A_D</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_HT1</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT1</t>
+          <t>Odd_marcar_prim_H</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT1</t>
+          <t>Odd_marcar_prim_A</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_H</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_DNB_A</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -742,18 +722,18 @@
       <c r="AC2" t="n">
         <v>0</v>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD2" t="n">
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -767,19 +747,7 @@
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>45895.5</v>
       </c>
     </row>
@@ -883,18 +851,18 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD3" t="n">
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="n">
-        <v>0</v>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -908,19 +876,7 @@
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="3" t="n">
+      <c r="AK3" s="3" t="n">
         <v>45895.52083333334</v>
       </c>
     </row>
@@ -945,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1024,18 +980,18 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD4" t="n">
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1049,19 +1005,7 @@
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" s="3" t="n">
+      <c r="AK4" s="3" t="n">
         <v>45895.54166666666</v>
       </c>
     </row>
@@ -1086,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1165,18 +1109,18 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD5" t="n">
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF5" t="n">
-        <v>0</v>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1190,19 +1134,7 @@
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" s="3" t="n">
+      <c r="AK5" s="3" t="n">
         <v>45895.54166666666</v>
       </c>
     </row>
@@ -1306,18 +1238,18 @@
       <c r="AC6" t="n">
         <v>0</v>
       </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD6" t="n">
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF6" t="n">
-        <v>0</v>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1331,19 +1263,7 @@
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" s="3" t="n">
+      <c r="AK6" s="3" t="n">
         <v>45895.54166666666</v>
       </c>
     </row>
@@ -1447,18 +1367,18 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD7" t="n">
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF7" t="n">
-        <v>0</v>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1472,19 +1392,7 @@
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="3" t="n">
+      <c r="AK7" s="3" t="n">
         <v>45895.57291666666</v>
       </c>
     </row>
@@ -1571,14 +1479,14 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.56</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>2.22</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
@@ -1588,18 +1496,18 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD8" t="n">
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="n">
-        <v>0</v>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1613,19 +1521,7 @@
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="3" t="n">
+      <c r="AK8" s="3" t="n">
         <v>45895.58333333334</v>
       </c>
     </row>
@@ -1640,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1729,18 +1625,18 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD9" t="n">
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -1754,19 +1650,7 @@
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="3" t="n">
+      <c r="AK9" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -1791,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1870,18 +1754,18 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD10" t="n">
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="n">
-        <v>0</v>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -1895,19 +1779,7 @@
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" s="3" t="n">
+      <c r="AK10" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -1932,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2011,18 +1883,18 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD11" t="n">
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2036,19 +1908,7 @@
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" s="3" t="n">
+      <c r="AK11" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -2152,18 +2012,18 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD12" t="n">
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="n">
-        <v>0</v>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2177,19 +2037,7 @@
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="3" t="n">
+      <c r="AK12" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -2214,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2293,18 +2141,18 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD13" t="n">
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2318,19 +2166,7 @@
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -2345,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2434,18 +2270,18 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD14" t="n">
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -2459,19 +2295,7 @@
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3" t="n">
+      <c r="AK14" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -2496,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2575,18 +2399,18 @@
       <c r="AC15" t="n">
         <v>0</v>
       </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD15" t="n">
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="n">
-        <v>0</v>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2600,19 +2424,7 @@
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3" t="n">
+      <c r="AK15" s="3" t="n">
         <v>45895.60416666666</v>
       </c>
     </row>
@@ -2716,18 +2528,18 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD16" t="n">
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF16" t="n">
-        <v>0</v>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2741,19 +2553,7 @@
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="3" t="n">
+      <c r="AK16" s="3" t="n">
         <v>45895.625</v>
       </c>
     </row>
@@ -2857,18 +2657,18 @@
       <c r="AC17" t="n">
         <v>0</v>
       </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD17" t="n">
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2882,19 +2682,7 @@
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO17" s="3" t="n">
+      <c r="AK17" s="3" t="n">
         <v>45895.625</v>
       </c>
     </row>
@@ -2998,18 +2786,18 @@
       <c r="AC18" t="n">
         <v>0</v>
       </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD18" t="n">
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="n">
-        <v>0</v>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -3023,19 +2811,7 @@
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="3" t="n">
+      <c r="AK18" s="3" t="n">
         <v>45895.63541666666</v>
       </c>
     </row>
@@ -3139,18 +2915,18 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD19" t="n">
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF19" t="n">
-        <v>0</v>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -3164,19 +2940,7 @@
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="3" t="n">
+      <c r="AK19" s="3" t="n">
         <v>45895.63541666666</v>
       </c>
     </row>
@@ -3280,18 +3044,18 @@
       <c r="AC20" t="n">
         <v>0</v>
       </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD20" t="n">
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="n">
-        <v>0</v>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -3305,19 +3069,7 @@
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="3" t="n">
+      <c r="AK20" s="3" t="n">
         <v>45895.66666666666</v>
       </c>
     </row>
@@ -3421,18 +3173,18 @@
       <c r="AC21" t="n">
         <v>0</v>
       </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="AD21" t="n">
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF21" t="n">
-        <v>0</v>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -3446,19 +3198,7 @@
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="3" t="n">
+      <c r="AK21" s="3" t="n">
         <v>45895.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.13</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>2.45</v>
       </c>
       <c r="N14" t="n">
-        <v>9.300000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>4.57</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.77</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="N15" t="n">
-        <v>5.68</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,10 +2121,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>4.5</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2692,27 +2692,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45895.63541666666</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="19">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45895.66666666666</v>
+        <v>45895.63541666666</v>
       </c>
     </row>
     <row r="21">
@@ -3199,6 +3199,135 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
+        <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45895.66666666666</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2649,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>6.2</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2475,10 +2475,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
         <v>1.47</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6.2</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,16 +2643,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,16 +3159,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,16 +3288,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3329,6 +3329,135 @@
       </c>
       <c r="AK22" s="3" t="n">
         <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M23" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45895.67708333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>5.7</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,16 +2514,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>2.62</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1323,34 +1323,34 @@
         <v>1.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Y7" t="n">
         <v>1.8</v>
@@ -1359,16 +1359,16 @@
         <v>2</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,77 +2088,77 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.38</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2484,52 +2484,52 @@
         <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
         <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,52 +2613,52 @@
         <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3129,34 +3129,34 @@
         <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Y21" t="n">
         <v>1.44</v>
@@ -3171,10 +3171,10 @@
         <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3258,52 +3258,52 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>2.62</v>
       </c>
       <c r="N10" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="S10" t="n">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.26</v>
+        <v>3.08</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>2.71</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.1</v>
+        <v>8</v>
       </c>
       <c r="R14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.57</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AA14" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>2.71</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.7</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>7.4</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>3.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.32</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>3.74</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.1</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.57</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q17" t="n">
         <v>8.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2742,13 +2742,13 @@
         <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
@@ -2757,19 +2757,19 @@
         <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W18" t="n">
         <v>1.32</v>
       </c>
       <c r="X18" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Y18" t="n">
         <v>2.07</v>
@@ -2778,10 +2778,10 @@
         <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
         <v>2.25</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45895.63541666666</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3129,52 +3129,52 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45895.66666666666</v>
+        <v>45895.63541666666</v>
       </c>
     </row>
     <row r="22">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,85 +3378,214 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.4</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>5.4</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>6.5</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
         <v>1.44</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.62</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA24" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB24" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45895.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>6.05</v>
       </c>
       <c r="R11" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.08</v>
+        <v>2.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.5</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="T12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.25</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.85</v>
+        <v>2.54</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.68</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>3.34</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2907,10 +2907,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45895.625</v>
+        <v>45895.63541666666</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45895.63541666666</v>
+        <v>45895.66666666666</v>
       </c>
     </row>
     <row r="22">
@@ -3337,27 +3337,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>1.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>1.81</v>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>6.03</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>6.09</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.25</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3457,135 +3457,6 @@
         <v>0</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>45895.66666666666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Afturelding</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
         <v>45895.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.18</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>2.54</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>8.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.74</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1590,10 +1590,10 @@
         <v>7</v>
       </c>
       <c r="R9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T9" t="n">
         <v>3.3</v>
@@ -1608,7 +1608,7 @@
         <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="Y9" t="n">
         <v>2.25</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.05</v>
+        <v>4.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>3.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.7</v>
+        <v>1.49</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>1.8</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
         <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X16" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>3.08</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1.71</v>
+        <v>7.37</v>
       </c>
       <c r="P17" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>3.58</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.34</v>
+        <v>1.06</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>1.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.98</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.83</v>
+        <v>6.05</v>
       </c>
       <c r="R14" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="U14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>7.37</v>
+        <v>1.71</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>2.71</v>
+        <v>3.8</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>1.38</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.06</v>
+        <v>3.34</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.71</v>
+        <v>7.37</v>
       </c>
       <c r="P18" t="n">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.8</v>
+        <v>2.71</v>
       </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>2.92</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.38</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>3.58</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.34</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3000,28 +3000,28 @@
         <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.86</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
         <v>1.16</v>
@@ -3030,10 +3030,10 @@
         <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
         <v>2.2</v>
@@ -3045,7 +3045,7 @@
         <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>4.83</v>
       </c>
       <c r="R10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH10" t="n">
-        <v>2.54</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8</v>
+        <v>7.37</v>
       </c>
       <c r="P16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.5</v>
+        <v>2.04</v>
       </c>
       <c r="R16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>3.08</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q17" t="n">
         <v>8.5</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.07</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.97</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.74</v>
+        <v>2.51</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>7.37</v>
+        <v>1.71</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>6.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S18" t="n">
-        <v>2.71</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3387,13 +3387,13 @@
         <v>6.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.03</v>
+        <v>5.32</v>
       </c>
       <c r="R23" t="n">
         <v>1.22</v>
@@ -3402,19 +3402,19 @@
         <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="Y23" t="n">
         <v>1.4</v>
@@ -3429,10 +3429,10 @@
         <v>1.88</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2100,25 +2100,25 @@
         <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.05</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>1.52</v>
@@ -2127,22 +2127,22 @@
         <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="AB13" t="n">
         <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
         <v>1.85</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O16" t="n">
-        <v>7.37</v>
+        <v>1.71</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.04</v>
+        <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>2.71</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="V16" t="n">
         <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>2.92</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.58</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>3.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,34 +2613,34 @@
         <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>2.97</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
         <v>2.05</v>
@@ -2649,16 +2649,16 @@
         <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U18" t="n">
         <v>1.32</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y18" t="n">
         <v>2.07</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.38</v>
-      </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.2</v>
       </c>
-      <c r="P21" t="n">
+      <c r="T21" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.3</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -693,7 +693,7 @@
         <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="U2" t="n">
         <v>1.2</v>
@@ -708,13 +708,13 @@
         <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
         <v>1.08</v>
@@ -723,7 +723,7 @@
         <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1983,13 +1983,13 @@
         <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.7</v>
@@ -1998,7 +1998,7 @@
         <v>2.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="Z12" t="n">
         <v>1.3</v>
@@ -2007,13 +2007,13 @@
         <v>6.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
         <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
         <v>1.58</v>
@@ -2226,7 +2226,7 @@
         <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
@@ -2235,7 +2235,7 @@
         <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
         <v>2.2</v>
@@ -2262,7 +2262,7 @@
         <v>1.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="AB14" t="n">
         <v>1.15</v>
@@ -2287,7 +2287,7 @@
         <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.9</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W18" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA18" t="n">
         <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC12" t="n">
         <v>2.3</v>
       </c>
-      <c r="M12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,28 +2484,28 @@
         <v>8.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="P16" t="n">
-        <v>2.95</v>
+        <v>2.64</v>
       </c>
       <c r="Q16" t="n">
         <v>6.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
         <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
         <v>1.13</v>
@@ -2514,7 +2514,7 @@
         <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="Z16" t="n">
         <v>2.65</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
         <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.74</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.9</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.74</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3393,19 +3393,19 @@
         <v>2.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.32</v>
+        <v>5.5</v>
       </c>
       <c r="R23" t="n">
         <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -3414,7 +3414,7 @@
         <v>1.11</v>
       </c>
       <c r="X23" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Y23" t="n">
         <v>1.4</v>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,34 +1452,34 @@
         <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y8" t="n">
         <v>1.8</v>
@@ -1488,16 +1488,16 @@
         <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>6.7</v>
       </c>
       <c r="M16" t="n">
-        <v>5.7</v>
+        <v>3.47</v>
       </c>
       <c r="N16" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O16" t="n">
-        <v>1.74</v>
+        <v>6.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.5</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>2.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6.5</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.42</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U21" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X21" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK23"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="N9" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>5.05</v>
       </c>
       <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.73</v>
       </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>3.14</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.3</v>
+        <v>2.03</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.039999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.41</v>
+        <v>5.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.88</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.7</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>4.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.47</v>
+        <v>9.5</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>2.05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.85</v>
+        <v>3.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V16" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.6</v>
+        <v>4.41</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.5</v>
+        <v>1.09</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.11</v>
+        <v>2.54</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45895.625</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="17">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45895.63541666666</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="20">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.45</v>
+        <v>1.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.08</v>
       </c>
       <c r="U21" t="n">
         <v>1.67</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>2.24</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45895.66666666666</v>
+        <v>45895.63541666666</v>
       </c>
     </row>
     <row r="22">
@@ -3337,126 +3337,255 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>16:15</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Valur</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Afturelding</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>1.4</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>5.4</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>6.5</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>1.79</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>2.75</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>5.5</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>1.22</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>4</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1.71</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>1.01</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>1.11</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>5.75</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y24" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z24" t="n">
         <v>2.75</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AA24" t="n">
         <v>1.92</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AB24" t="n">
         <v>1.88</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AC24" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AD24" t="n">
         <v>2.15</v>
       </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.15</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH24" t="n">
         <v>3.1</v>
       </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45895.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -678,13 +678,13 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.58</v>
@@ -699,7 +699,7 @@
         <v>1.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.57</v>
@@ -708,13 +708,13 @@
         <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
         <v>1.08</v>
@@ -723,7 +723,7 @@
         <v>2.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.02</v>
+        <v>2.59</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.14</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.5</v>
+        <v>4.41</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="N16" t="n">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.039999999999999</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="V16" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.54</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,7 +2613,7 @@
         <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
@@ -2634,7 +2634,7 @@
         <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
         <v>1.39</v>
@@ -2652,10 +2652,10 @@
         <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
         <v>1.48</v>
@@ -2733,19 +2733,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
         <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="P18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="Q18" t="n">
         <v>6.5</v>
@@ -2757,7 +2757,7 @@
         <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
         <v>1.73</v>
@@ -2778,10 +2778,10 @@
         <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
         <v>1.75</v>
@@ -2892,7 +2892,7 @@
         <v>1.33</v>
       </c>
       <c r="V19" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
         <v>1.31</v>
@@ -3138,19 +3138,19 @@
         <v>4.82</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
         <v>3.48</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="O24" t="n">
         <v>1.79</v>
@@ -3528,7 +3528,7 @@
         <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -3540,7 +3540,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
         <v>5.75</v>
@@ -3552,10 +3552,10 @@
         <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.039999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V12" t="n">
         <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.41</v>
+        <v>5.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.57</v>
+        <v>1.88</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
         <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.15</v>
+        <v>4.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>2.57</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="N18" t="n">
         <v>8.5</v>
@@ -2778,10 +2778,10 @@
         <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
         <v>1.75</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="N24" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.79</v>
@@ -3552,10 +3552,10 @@
         <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -669,25 +669,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M2" t="n">
         <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
         <v>2.29</v>
@@ -705,7 +705,7 @@
         <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="Y2" t="n">
         <v>2.8</v>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.88</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>7.08</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>1.77</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.9</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
         <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.32</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.42</v>
+        <v>1.98</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.7</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>5.7</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q19" t="n">
         <v>6.5</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.05</v>
-      </c>
       <c r="R19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y19" t="n">
         <v>1.42</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.07</v>
-      </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="O21" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
         <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
         <v>3.48</v>
       </c>
       <c r="T21" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
         <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="Y21" t="n">
         <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
         <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
         <v>3.96</v>
@@ -705,7 +705,7 @@
         <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="Y2" t="n">
         <v>2.8</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.039999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.47</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z11" t="n">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.57</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
         <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.15</v>
+        <v>4.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>2.63</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>7.08</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
         <v>3.75</v>
       </c>
-      <c r="N17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.55</v>
-      </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.28</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4.75</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.5</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
         <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,19 +3507,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="M24" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="P24" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
         <v>5.5</v>
@@ -3528,7 +3528,7 @@
         <v>1.22</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -3546,16 +3546,16 @@
         <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
         <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="N9" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.5</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.08</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q18" t="n">
         <v>6.5</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.05</v>
-      </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.85</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -678,28 +678,28 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
         <v>2.29</v>
       </c>
       <c r="T2" t="n">
-        <v>3.88</v>
+        <v>3.74</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
         <v>1.57</v>
@@ -708,22 +708,22 @@
         <v>2.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AA2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB2" t="n">
         <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
         <v>2.3</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Y15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="O17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q17" t="n">
         <v>6.5</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.05</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>1.37</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>2.65</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.62</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
         <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>2.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2871,13 +2871,13 @@
         <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
@@ -2886,13 +2886,13 @@
         <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
         <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
         <v>1.39</v>
@@ -2910,7 +2910,7 @@
         <v>3.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
         <v>2.85</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.77</v>
@@ -3540,22 +3540,22 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X24" t="n">
         <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M8" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>4.98</v>
+        <v>4.65</v>
       </c>
       <c r="O8" t="n">
         <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.05</v>
+        <v>5.15</v>
       </c>
       <c r="R8" t="n">
         <v>1.3</v>
@@ -1470,7 +1470,7 @@
         <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
@@ -1479,19 +1479,19 @@
         <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="Y8" t="n">
         <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC8" t="n">
         <v>1.73</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.039999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.41</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.5</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.39</v>
       </c>
       <c r="X15" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.19</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>6.2</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1.61</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.5</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
         <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.11</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,49 +2733,49 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>7.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA18" t="n">
         <v>3.6</v>
@@ -2784,10 +2784,10 @@
         <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="P19" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,19 +3507,19 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="M24" t="n">
         <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>1.77</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
         <v>5.5</v>
@@ -3546,16 +3546,16 @@
         <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
         <v>3.74</v>
@@ -702,28 +702,28 @@
         <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,58 +1704,58 @@
         <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.47</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>11.3</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>1.79</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.05</v>
+        <v>10.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
-        <v>2.9</v>
+        <v>3.34</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>2.5</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.11</v>
+        <v>3.32</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>5.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>7.1</v>
       </c>
       <c r="P18" t="n">
-        <v>2.49</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.5</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.42</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
         <v>3.7</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,58 +1704,58 @@
         <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.3</v>
       </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>9.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.5</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>4.41</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.75</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>7.1</v>
+        <v>1.61</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>2.65</v>
       </c>
       <c r="Q18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.16</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.1</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.2</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.16</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>5.75</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>1.6</v>
       </c>
       <c r="O19" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z19" t="n">
         <v>1.61</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.65</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>4.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M23" t="n">
         <v>3.45</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -675,22 +675,22 @@
         <v>2.92</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="O2" t="n">
-        <v>3.98</v>
+        <v>3.82</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="T2" t="n">
         <v>3.74</v>
@@ -699,31 +699,31 @@
         <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X2" t="n">
         <v>2.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AA2" t="n">
         <v>5.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
         <v>2.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="M9" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.43</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2.18</v>
       </c>
-      <c r="P9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>5.5</v>
@@ -1725,7 +1725,7 @@
         <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U10" t="n">
         <v>1.26</v>
@@ -1746,7 +1746,7 @@
         <v>1.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AB10" t="n">
         <v>1.15</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
         <v>1.88</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.2</v>
       </c>
-      <c r="N12" t="n">
-        <v>4.6</v>
-      </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>9.5</v>
+        <v>4.15</v>
       </c>
       <c r="O14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.58</v>
+        <v>1.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.41</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
         <v>3.1</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.21</v>
+        <v>3.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.5</v>
+        <v>5.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,62 +2604,62 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>11.3</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.79</v>
+        <v>1.59</v>
       </c>
       <c r="P17" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.1</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.91</v>
+        <v>1.97</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.75</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.95</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AE17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="O18" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>6.5</v>
+        <v>10.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>1.88</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2868,37 +2868,37 @@
         <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O19" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="T19" t="n">
         <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="X19" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="Y19" t="n">
         <v>2.2</v>
@@ -2910,13 +2910,13 @@
         <v>4.16</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O20" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="P20" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.65</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>3.48</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
         <v>1.63</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.85</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
         <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB20" t="n">
         <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AH20" t="n">
         <v>2.3</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.45</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>5.03</v>
       </c>
       <c r="O24" t="n">
         <v>1.77</v>
@@ -3525,13 +3525,13 @@
         <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="U24" t="n">
         <v>1.71</v>
@@ -3540,7 +3540,7 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
         <v>5.75</v>
@@ -3549,10 +3549,10 @@
         <v>1.38</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB24" t="n">
         <v>1.72</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="M2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
         <v>3.82</v>
@@ -702,10 +702,10 @@
         <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Y2" t="n">
         <v>2.59</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2.55</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.43</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.33</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.47</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="X8" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>2.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>1.49</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N9" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.2</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>2.6</v>
       </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>4</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD9" t="n">
         <v>1.93</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.05</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T12" t="n">
         <v>3.3</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.49</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
         <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.07</v>
+        <v>1.58</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.8</v>
+        <v>4.46</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.53</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.25</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,77 +2088,77 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.73</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC15" t="n">
         <v>2.4</v>
       </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.54</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,37 +2475,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
         <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>1.55</v>
@@ -2514,22 +2514,22 @@
         <v>2.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.25</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>13</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.6</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.36</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.34</v>
-      </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.07</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,77 +2862,77 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.75</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>1.62</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>1.74</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>10.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH19" t="n">
         <v>3.1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.07</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.55</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>4.06</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
         <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.55</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T21" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK24"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>5.09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AA8" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45895.58333333334</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="M9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S9" t="n">
         <v>3.75</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.2</v>
-      </c>
       <c r="T9" t="n">
-        <v>2.6</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45895.58333333334</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>6.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="N10" t="n">
-        <v>5.8</v>
+        <v>1.47</v>
       </c>
       <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.55</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="T10" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.2</v>
+        <v>4.16</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.88</v>
+        <v>1.07</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2.05</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.19</v>
+        <v>2.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>1.06</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>2.87</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>2.07</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>3.7</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.46</v>
+        <v>2.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.27</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.54</v>
+        <v>1.22</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.66666666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>3.45</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O13" t="n">
         <v>3.2</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>3.24</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.25</v>
+        <v>2.76</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Valur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,78 +2217,78 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>5.03</v>
       </c>
       <c r="O14" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH14" t="n">
         <v>3.1</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
@@ -2296,1296 +2296,6 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45895.60416666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>South Africa Premier Soccer League</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Polokwane City</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Durban City</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>45895.60416666666</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>South Africa Premier Soccer League</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TS Galaxy</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Siwelele</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>45895.60416666666</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Víkingur Reykjavík</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Vestri</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>8</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45895.625</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Egypt Egyptian Premier League</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Haras El Hodood</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Al Masry</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="O18" t="n">
-        <v>6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
-        <v>45895.625</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Egypt Egyptian Premier League</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Zamalek</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Pharco</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="3" t="n">
-        <v>45895.625</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Switzerland Challenge League</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bellinzona</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Yverdon Sport</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3" t="n">
-        <v>45895.63541666666</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Switzerland Challenge League</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Étoile Carouge</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Stade Nyonnais</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4</v>
-      </c>
-      <c r="N21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
-        <v>45895.63541666666</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Paphos</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Red Star Belgrade</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
-        <v>45895.66666666666</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sturm Graz</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>FK Bodo - Glimt</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X23" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="3" t="n">
-        <v>45895.66666666666</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Iceland Úrvalsdeild</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Valur</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Afturelding</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X24" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="3" t="n">
         <v>45895.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.75</v>
+        <v>4.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="T4" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.55</v>
+        <v>3.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="M5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2.55</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>4.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="M8" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="O8" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.65</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.62</v>
+        <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45895.60416666666</v>
+        <v>45895.58333333334</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="M9" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="N9" t="n">
-        <v>8.5</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>1.59</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>3.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>3.75</v>
+        <v>2.49</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.65</v>
+        <v>1.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.07</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.4</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45895.625</v>
+        <v>45895.58333333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,78 +1701,78 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.05</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.33</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA10" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45895.625</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.6</v>
+        <v>3.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>2.75</v>
+        <v>3.24</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.68</v>
+        <v>2.07</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>2.25</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45895.625</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="N12" t="n">
-        <v>2.07</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>5.09</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>3.65</v>
       </c>
       <c r="U12" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.65</v>
+        <v>2.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.22</v>
+        <v>1.66</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45895.66666666666</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.1</v>
+        <v>4.15</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.43</v>
+        <v>3.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45895.66666666666</v>
+        <v>45895.60416666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,27 +2176,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valur</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,85 +2217,1375 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>5.03</v>
+        <v>5.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
         <v>5.5</v>
       </c>
       <c r="R14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45895.60416666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orbit College</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>7</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45895.60416666666</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>South Africa Premier Soccer League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Richards Bay</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Chippa United</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45895.60416666666</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vestri</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45895.625</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Zamalek</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pharco</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45895.625</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Haras El Hodood</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Al Masry</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45895.625</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Switzerland Challenge League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Étoile Carouge</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stade Nyonnais</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
+        <v>45895.63541666666</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Switzerland Challenge League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bellinzona</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yverdon Sport</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45895.63541666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sturm Graz</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>FK Bodo - Glimt</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X22" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
+        <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Paphos</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Red Star Belgrade</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3" t="n">
+        <v>45895.66666666666</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Iceland Úrvalsdeild</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Valur</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Afturelding</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N24" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R24" t="n">
         <v>1.18</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S24" t="n">
         <v>4</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T24" t="n">
         <v>2.18</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U24" t="n">
         <v>1.71</v>
       </c>
-      <c r="V14" t="n">
+      <c r="V24" t="n">
         <v>1.01</v>
       </c>
-      <c r="W14" t="n">
+      <c r="W24" t="n">
         <v>1.13</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X24" t="n">
         <v>5.75</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y24" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z24" t="n">
         <v>2.7</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AA24" t="n">
         <v>2.1</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AB24" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC24" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD24" t="n">
         <v>2.15</v>
       </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
         <v>1.15</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AH24" t="n">
         <v>3.1</v>
       </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3" t="n">
         <v>45895.67708333334</v>
       </c>
     </row>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -678,19 +678,19 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.82</v>
+        <v>3.98</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.58</v>
       </c>
       <c r="S2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="T2" t="n">
         <v>3.74</v>
@@ -699,7 +699,7 @@
         <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
         <v>1.57</v>
@@ -723,7 +723,7 @@
         <v>2.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AH2" t="n">
         <v>1.33</v>
@@ -942,7 +942,7 @@
         <v>1.71</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.61</v>
+        <v>4.4</v>
       </c>
       <c r="R4" t="n">
         <v>1.72</v>
@@ -957,7 +957,7 @@
         <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
         <v>1.65</v>
@@ -972,7 +972,7 @@
         <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB4" t="n">
         <v>1.06</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="M9" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
         <v>3.08</v>
@@ -1611,10 +1611,10 @@
         <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
         <v>3.9</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.04</v>
+        <v>3.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.86</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,62 +1830,62 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>3.24</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>2.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.07</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.8</v>
+        <v>5.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD11" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O12" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.15</v>
+        <v>9.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.09</v>
+        <v>2.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.84</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>5.09</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AA14" t="n">
         <v>5.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.5</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.4</v>
       </c>
-      <c r="X15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH15" t="n">
-        <v>2.54</v>
+        <v>1.63</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.21</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="O17" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="P17" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.68</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>3.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M18" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O18" t="n">
-        <v>1.74</v>
+        <v>6.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.6</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.36</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6.7</v>
+        <v>1.19</v>
       </c>
       <c r="M19" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="N19" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>7.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.16</v>
+        <v>1.93</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>3.19</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.47</v>
       </c>
       <c r="N20" t="n">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.08</v>
+        <v>3.33</v>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="V20" t="n">
         <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,37 +3120,37 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
         <v>3.55</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.34</v>
-      </c>
       <c r="T21" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
         <v>1.12</v>
@@ -3159,22 +3159,22 @@
         <v>4.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.35</v>
+        <v>2.56</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.77</v>
@@ -3528,10 +3528,10 @@
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="T24" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>1.71</v>
@@ -3540,22 +3540,22 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X24" t="n">
         <v>5.75</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>2.47</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.47</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2.3</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
         <v>1.3</v>
       </c>
-      <c r="AA10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,37 +1959,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M12" t="n">
         <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.55</v>
@@ -1998,22 +1998,22 @@
         <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4.05</v>
+        <v>2.85</v>
       </c>
       <c r="N13" t="n">
-        <v>9.5</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>7</v>
+        <v>5.09</v>
       </c>
       <c r="R13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="X13" t="n">
         <v>2.4</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="Y13" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.46</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.09</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.77</v>
+        <v>1.66</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.55</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.62</v>
+        <v>3.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.58</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.63</v>
+        <v>2.77</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,77 +2475,77 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>3.19</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.71</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>3.92</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.7</v>
+        <v>5.15</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y4" t="n">
         <v>2.55</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.47</v>
+        <v>1.63</v>
       </c>
       <c r="M8" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>4.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>1.97</v>
+        <v>2.23</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.64</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>2.73</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.9</v>
+        <v>2.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.63</v>
+        <v>2.47</v>
       </c>
       <c r="M9" t="n">
-        <v>3.62</v>
+        <v>3.14</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>2.65</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.23</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>3.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>2.49</v>
       </c>
       <c r="T9" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W9" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.84</v>
+        <v>3.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M10" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.19</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.71</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>2.52</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>3.92</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.63</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.95</v>
+        <v>9.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.21</v>
+        <v>2.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.58</v>
+        <v>2.77</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,37 +1959,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M12" t="n">
         <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>1.55</v>
@@ -1998,22 +1998,22 @@
         <v>2.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N14" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="X14" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>4.05</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>3.19</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>2.69</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>3.71</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.3</v>
+        <v>2.52</v>
       </c>
       <c r="U15" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="X15" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.7</v>
       </c>
-      <c r="Y15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>2.3</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.09</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.77</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.49</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="N17" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="O17" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.9</v>
       </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.75</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.6</v>
+        <v>4.16</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.06</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,77 +2733,77 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>1.19</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>6.2</v>
       </c>
       <c r="N18" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>6.5</v>
+        <v>1.57</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>7.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.07</v>
       </c>
-      <c r="W18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.45</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -678,19 +678,19 @@
         <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.98</v>
+        <v>4.14</v>
       </c>
       <c r="P2" t="n">
         <v>1.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
         <v>3.74</v>
@@ -699,7 +699,7 @@
         <v>1.21</v>
       </c>
       <c r="V2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
         <v>1.57</v>
@@ -714,16 +714,16 @@
         <v>1.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC2" t="n">
         <v>2.16</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.33</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>6.44</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
         <v>1.86</v>
@@ -945,43 +945,43 @@
         <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.6</v>
+        <v>4.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC4" t="n">
         <v>2.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.42</v>
+        <v>2.8</v>
       </c>
       <c r="M5" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
         <v>1.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>4.35</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="X5" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1443,19 +1443,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.4</v>
+        <v>4.87</v>
       </c>
       <c r="O8" t="n">
         <v>2.2</v>
       </c>
       <c r="P8" t="n">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
         <v>4.75</v>
@@ -1467,37 +1467,37 @@
         <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
         <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X8" t="n">
-        <v>3.6</v>
+        <v>3.44</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC8" t="n">
         <v>1.73</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.47</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="N9" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.64</v>
+        <v>4.43</v>
       </c>
       <c r="R9" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,28 +1710,28 @@
         <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
         <v>1.55</v>
@@ -1746,16 +1746,16 @@
         <v>1.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1845,10 +1845,10 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
         <v>2.4</v>
@@ -1857,7 +1857,7 @@
         <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
         <v>1.03</v>
@@ -1866,7 +1866,7 @@
         <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y11" t="n">
         <v>2.25</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.77</v>
+        <v>2.58</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>4.15</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="X12" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.09</v>
+        <v>3.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,77 +2088,77 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>2.85</v>
+        <v>3.47</v>
       </c>
       <c r="N13" t="n">
-        <v>4.2</v>
+        <v>3.19</v>
       </c>
       <c r="O13" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q13" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.62</v>
-      </c>
       <c r="Z13" t="n">
-        <v>1.43</v>
+        <v>1.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="AD13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.66</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,58 +2217,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="M14" t="n">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="N14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
         <v>4.75</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="X14" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AD14" t="n">
         <v>1.47</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.19</v>
+        <v>5.8</v>
       </c>
       <c r="O15" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.71</v>
+        <v>6.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
-        <v>3.92</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.63</v>
+        <v>2.65</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,77 +2604,77 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.7</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>3.47</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>6.5</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="AB17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.07</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.19</v>
+        <v>5.2</v>
       </c>
       <c r="M18" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>10</v>
+        <v>1.67</v>
       </c>
       <c r="O18" t="n">
-        <v>1.57</v>
+        <v>6.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.7</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>2.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.93</v>
+        <v>3.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
@@ -2886,13 +2886,13 @@
         <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
         <v>1.39</v>
@@ -2907,13 +2907,13 @@
         <v>1.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.6</v>
+        <v>3.97</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.48</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.19</v>
+        <v>1.54</v>
       </c>
       <c r="M20" t="n">
-        <v>3.47</v>
+        <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.33</v>
+        <v>2.11</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U20" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>2.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,62 +3120,62 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.54</v>
+        <v>3.19</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.47</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.39</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="R21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.25</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="X21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.15</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M23" t="n">
         <v>3.45</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3507,16 +3507,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="P24" t="n">
         <v>2.65</v>
@@ -3528,7 +3528,7 @@
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>3.66</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
@@ -3540,22 +3540,22 @@
         <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X24" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>1.62</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -652,94 +652,94 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2.8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="O2" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.59</v>
       </c>
       <c r="Z2" t="n">
         <v>1.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.55</v>
+        <v>5.97</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '90+1']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="N4" t="n">
-        <v>4.55</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1039,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '35', '60', '90+3']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '12', '64', '87']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.05</v>
+        <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.69</v>
+        <v>2.03</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="N8" t="n">
-        <v>4.87</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.43</v>
       </c>
       <c r="R8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.3</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH8" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>1.69</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>4.87</v>
       </c>
       <c r="O9" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.27</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="X9" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.37</v>
+        <v>1.73</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.71</v>
+        <v>1.91</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.38</v>
+        <v>1.8</v>
       </c>
       <c r="M11" t="n">
-        <v>4.05</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>9.5</v>
+        <v>5.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.58</v>
+        <v>1.42</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.58</v>
+        <v>1.88</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.3</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="N12" t="n">
-        <v>3.95</v>
+        <v>9.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.2</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AC12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.16</v>
       </c>
-      <c r="W12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>2.58</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>3.19</v>
+        <v>4.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1.32</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="M14" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>2.15</v>
+        <v>3.73</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>1.79</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AA14" t="n">
-        <v>7</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.06</v>
+        <v>1.41</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="N15" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.8</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.58</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.88</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>2.16</v>
       </c>
       <c r="N16" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.22</v>
+        <v>6.73</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5</v>
+        <v>3.68</v>
       </c>
       <c r="N17" t="n">
-        <v>8.5</v>
+        <v>1.51</v>
       </c>
       <c r="O17" t="n">
-        <v>1.69</v>
+        <v>6.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.2</v>
+        <v>2.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X17" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>3.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.2</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>6.98</v>
+        <v>1.85</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>8</v>
       </c>
       <c r="R18" t="n">
         <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.94</v>
+        <v>3.85</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>2.45</v>
+        <v>1.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA19" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>3.97</v>
-      </c>
       <c r="AB19" t="n">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="O20" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="P20" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
         <v>1.24</v>
@@ -3015,7 +3015,7 @@
         <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="U20" t="n">
         <v>1.62</v>
@@ -3027,41 +3027,41 @@
         <v>1.12</v>
       </c>
       <c r="X20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH20" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.25</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.19</v>
+        <v>4.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.4</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.71</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
         <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.61</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AD21" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.45</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S22" t="n">
         <v>3.2</v>
       </c>
-      <c r="P22" t="n">
+      <c r="T22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V22" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X22" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X23" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.05</v>
+        <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>2.97</v>
+        <v>3.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,103 +1030,103 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>2.68</v>
+        <v>2.97</v>
       </c>
       <c r="N5" t="n">
-        <v>2.85</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['21', '35', '60', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['3', '12', '64', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,103 +1159,103 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="N6" t="n">
-        <v>4.55</v>
+        <v>2.85</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="S6" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>4.35</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="X6" t="n">
-        <v>2.51</v>
+        <v>1.87</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.65</v>
+        <v>6.45</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '35', '60', '90+3']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '12', '64', '87']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.96</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['83', '90+6']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71', '79']</t>
         </is>
       </c>
       <c r="AG8" t="n">
@@ -1555,20 +1555,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '71']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1675,103 +1675,103 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="P10" t="n">
         <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="T10" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="U10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.16</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.57</v>
+        <v>2.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
+          <t>['45+4']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="N11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.8</v>
+        <v>4.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="X11" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1955,29 +1955,29 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="N12" t="n">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
         <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
         <v>2.4</v>
@@ -1986,22 +1986,22 @@
         <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AA12" t="n">
         <v>4.1</v>
@@ -2017,19 +2017,19 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2071,94 +2071,94 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="N13" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.09</v>
+        <v>2.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
+          <t>['22', '45+1']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2200,20 +2200,20 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '27', '63']</t>
         </is>
       </c>
       <c r="AG14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -2361,46 +2361,46 @@
         <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="T15" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
         <v>1.7</v>
       </c>
       <c r="X15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AA15" t="n">
         <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -2471,69 +2471,69 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.05</v>
+        <v>1.58</v>
       </c>
       <c r="M16" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O16" t="n">
-        <v>2.85</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>7.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2545,7 +2545,7 @@
         <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="M18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="O18" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="N19" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="O19" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="T19" t="n">
-        <v>2.06</v>
+        <v>2.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="X19" t="n">
-        <v>5.5</v>
+        <v>2.74</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>2.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>3.85</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.26</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2974,20 +2974,20 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG20" t="n">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paphos</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.87</v>
+        <v>3.45</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>2.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.41</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paphos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,61 +3378,61 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="M23" t="n">
         <v>3.45</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="N23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
         <v>3.2</v>
       </c>
-      <c r="P23" t="n">
+      <c r="T23" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U23" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="V23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="X23" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
@@ -3445,10 +3445,10 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>

--- a/jogos_2025-08-26.xlsx
+++ b/jogos_2025-08-26.xlsx
@@ -910,20 +910,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -985,12 +985,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '49', '90+4']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '23', '45+2']</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1555,82 +1555,82 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N9" t="n">
-        <v>4.87</v>
+        <v>4.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['1', '71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,81 +1826,81 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="M11" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="R11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.65</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,20 +1933,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orbit College</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -1959,77 +1959,77 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.25</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>5</v>
+        <v>2.16</v>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U12" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.02</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.95</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,103 +2062,103 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TS Galaxy</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Siwelele</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="M13" t="n">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.96</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2.18</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['22', '45+1']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '27', '63']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>TS Galaxy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Siwelele</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X14" t="n">
         <v>2.2</v>
       </c>
-      <c r="M14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Y14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Z14" t="n">
         <v>1.35</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>5.65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['22', '45+1']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['21', '27', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,16 +2320,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>Orbit College</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2346,77 +2346,77 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>2.65</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.25</v>
+        <v>13</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
-        <v>2.04</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.08</v>
+        <v>2.02</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
         <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
+          <t>['56']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.09</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2568,113 +2568,113 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Masry</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.73</v>
+        <v>1.22</v>
       </c>
       <c r="M17" t="n">
-        <v>3.68</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>1.51</v>
+        <v>8.5</v>
       </c>
       <c r="O17" t="n">
-        <v>6.98</v>
+        <v>1.69</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="AB17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['5', '13', '62', '80']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['76']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.07</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.1</v>
+        <v>3.4</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,113 +2697,113 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>Al Masry</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.22</v>
+        <v>6.73</v>
       </c>
       <c r="M18" t="n">
-        <v>5.5</v>
+        <v>3.68</v>
       </c>
       <c r="N18" t="n">
-        <v>8.5</v>
+        <v>1.51</v>
       </c>
       <c r="O18" t="n">
-        <v>1.69</v>
+        <v>6.98</v>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>7.2</v>
+        <v>2.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="T18" t="n">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="X18" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>2.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.05</v>
+        <v>3.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.07</v>
+        <v>2.45</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3490,20 +3490,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '57', '60', '77']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '42', '90']</t>
         </is>
       </c>
       <c r="AG24" t="n">
